--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -958,7 +958,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>di-Methylation</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Double Carbamidomethylation</t>
+          <t>ubiquitinylation residue</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3390,7 +3390,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>ubiquitinylation residue</t>
+          <t>Double Carbamidomethylation</t>
         </is>
       </c>
       <c r="B40" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -958,7 +958,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>ubiquitinylation residue</t>
+          <t>Double Carbamidomethylation</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3390,7 +3390,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Double Carbamidomethylation</t>
+          <t>ubiquitinylation residue</t>
         </is>
       </c>
       <c r="B40" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -2326,7 +2326,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2402,7 +2402,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B27" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -958,7 +958,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>di-Methylation</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by calcium</t>
+          <t>Replacement of proton by potassium</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3998,7 +3998,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton by potassium</t>
+          <t>Replacement of 2 protons by calcium</t>
         </is>
       </c>
       <c r="B48" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -3922,7 +3922,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton by potassium</t>
+          <t>Replacement of 2 protons by calcium</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3998,7 +3998,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by calcium</t>
+          <t>Replacement of proton by potassium</t>
         </is>
       </c>
       <c r="B48" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -1034,7 +1034,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2402,7 +2402,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B27" t="n">

--- a/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
+++ b/Dependencies/Takasugi_2024/PTM_heatmap_df.xlsx
@@ -958,7 +958,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>di-Methylation</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>Acetaldehyde +28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +28</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton by potassium</t>
+          <t>Replacement of 2 protons by calcium</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3998,7 +3998,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by calcium</t>
+          <t>Replacement of proton by potassium</t>
         </is>
       </c>
       <c r="B48" t="n">
